--- a/tools/importer/reports/import-category-landing.report.xlsx
+++ b/tools/importer/reports/import-category-landing.report.xlsx
@@ -64,7 +64,7 @@
     <t>global/en/about-nzmp/global-ingredients.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-category","cards-value","cards-teaser"]</t>
+    <t>["columns-banner","columns-feature","cards-category","cards-category","cards-value","cards-teaser"]</t>
   </si>
   <si>
     <t>global/en/about-nzmp/global-ingredients</t>
@@ -73,7 +73,7 @@
     <t>category-landing</t>
   </si>
   <si>
-    <t>2026-08-13T23:45:38.779Z</t>
+    <t>2026-08-14T01:58:17.729Z</t>
   </si>
   <si>
     <t>NZMP's Global Ingredients Network | NZMP.com</t>
@@ -85,13 +85,13 @@
     <t>global/en/about-nzmp/news.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb"]</t>
+    <t>[]</t>
   </si>
   <si>
     <t>global/en/about-nzmp/news</t>
   </si>
   <si>
-    <t>2026-08-13T23:46:31.458Z</t>
+    <t>2026-08-14T01:59:13.866Z</t>
   </si>
   <si>
     <t>NZMP Newsfeed: News, Updates &amp; Events | NZMP.com</t>
@@ -103,13 +103,13 @@
     <t>global/en/about-nzmp/our-way-of-farming.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
   </si>
   <si>
     <t>global/en/about-nzmp/our-way-of-farming</t>
   </si>
   <si>
-    <t>2026-08-13T23:46:41.127Z</t>
+    <t>2026-08-14T01:59:23.761Z</t>
   </si>
   <si>
     <t>Our Way of Farming | NZMP.com</t>
@@ -121,13 +121,13 @@
     <t>global/en/about-nzmp/safety-and-quality.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","cards-value"]</t>
+    <t>["columns-banner","cards-value"]</t>
   </si>
   <si>
     <t>global/en/about-nzmp/safety-and-quality</t>
   </si>
   <si>
-    <t>2026-08-13T23:46:51.860Z</t>
+    <t>2026-08-14T01:59:36.070Z</t>
   </si>
   <si>
     <t>NZMP Ingredient Safety &amp; Quality Processes | NZMP.com</t>
@@ -139,13 +139,13 @@
     <t>global/en/applications/active-lifestyle.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-feature","cards-teaser"]</t>
+    <t>["columns-feature","cards-teaser"]</t>
   </si>
   <si>
     <t>global/en/applications/active-lifestyle</t>
   </si>
   <si>
-    <t>2026-08-13T23:47:01.179Z</t>
+    <t>2026-08-14T01:59:45.531Z</t>
   </si>
   <si>
     <t>Active Lifestyle | NZMP Dairy Ingredients | NZMP.com</t>
@@ -157,13 +157,13 @@
     <t>global/en/applications/beverages.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
+    <t>["columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
   </si>
   <si>
     <t>global/en/applications/beverages</t>
   </si>
   <si>
-    <t>2026-08-13T23:47:11.096Z</t>
+    <t>2026-08-14T01:59:56.784Z</t>
   </si>
   <si>
     <t>Beverages | NZMP.com</t>
@@ -178,7 +178,7 @@
     <t>global/en/applications/consumer-milk-powders</t>
   </si>
   <si>
-    <t>2026-08-13T23:47:19.849Z</t>
+    <t>2026-08-14T02:00:06.565Z</t>
   </si>
   <si>
     <t>Consumer Milk Powders | NZMP Dairy Ingredients | NZMP.com</t>
@@ -190,13 +190,13 @@
     <t>global/en/applications/food-manufacture.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-feature"]</t>
+    <t>["columns-feature"]</t>
   </si>
   <si>
     <t>global/en/applications/food-manufacture</t>
   </si>
   <si>
-    <t>2026-08-13T23:47:30.462Z</t>
+    <t>2026-08-14T02:00:16.402Z</t>
   </si>
   <si>
     <t>Food Manufacture | NZMP Dairy Ingredients | NZMP.com</t>
@@ -208,13 +208,13 @@
     <t>global/en/applications/medical-nutrition.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-feature","cards-value","cards-teaser"]</t>
+    <t>["columns-feature","cards-value","cards-teaser"]</t>
   </si>
   <si>
     <t>global/en/applications/medical-nutrition</t>
   </si>
   <si>
-    <t>2026-08-13T23:47:39.833Z</t>
+    <t>2026-08-14T02:00:28.530Z</t>
   </si>
   <si>
     <t>Medical Nutrition | NZMP Dairy Ingredients | NZMP.com</t>
@@ -229,7 +229,7 @@
     <t>global/en/applications/paediatric-nutrition</t>
   </si>
   <si>
-    <t>2026-08-13T23:48:03.662Z</t>
+    <t>2026-08-14T02:00:54.368Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/applications/paediatric-nutrition.html</t>
@@ -238,13 +238,13 @@
     <t>global/en/applications/yoghurts-and-cultured-products.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-feature","columns-feature","cards-value","cards-teaser"]</t>
+    <t>["columns-feature","columns-feature","cards-value","cards-teaser"]</t>
   </si>
   <si>
     <t>global/en/applications/yoghurts-and-cultured-products</t>
   </si>
   <si>
-    <t>2026-08-13T23:48:17.092Z</t>
+    <t>2026-08-14T02:01:05.942Z</t>
   </si>
   <si>
     <t>Yoghurts and Cultured Products | NZMP.com</t>
@@ -259,7 +259,7 @@
     <t>global/en/solutions/innovation-and-ingenuity</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:04.268Z</t>
+    <t>2026-08-14T02:07:43.090Z</t>
   </si>
   <si>
     <t>Innovation and Expertise | NZMP.com</t>
@@ -271,13 +271,13 @@
     <t>global/en/solutions/price-risk-management.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-value","cards-value"]</t>
+    <t>["columns-banner","columns-feature","cards-category","cards-value","cards-value"]</t>
   </si>
   <si>
     <t>global/en/solutions/price-risk-management</t>
   </si>
   <si>
-    <t>2026-08-13T23:55:19.165Z</t>
+    <t>2026-08-14T02:08:55.313Z</t>
   </si>
   <si>
     <t>Price Risk Management | NZMP.com</t>
@@ -289,13 +289,13 @@
     <t>global/en/solutions/third-party-manufacturing.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-value"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","cards-value"]</t>
   </si>
   <si>
     <t>global/en/solutions/third-party-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-13T23:55:26.273Z</t>
+    <t>2026-08-14T02:09:01.758Z</t>
   </si>
   <si>
     <t>Third Party Manufacturing | NZMP.com</t>
@@ -310,7 +310,7 @@
     <t>global/en/about-nzmp/global-ingredients/our-australian-ingredients</t>
   </si>
   <si>
-    <t>2026-08-13T23:45:46.523Z</t>
+    <t>2026-08-14T01:58:27.322Z</t>
   </si>
   <si>
     <t>Our Australian Ingredients | NZMP.com</t>
@@ -322,13 +322,13 @@
     <t>global/en/about-nzmp/global-ingredients/our-european-ingredients.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-value"]</t>
+    <t>["columns-banner","columns-feature","cards-category","cards-value"]</t>
   </si>
   <si>
     <t>global/en/about-nzmp/global-ingredients/our-european-ingredients</t>
   </si>
   <si>
-    <t>2026-08-13T23:45:56.282Z</t>
+    <t>2026-08-14T01:58:37.159Z</t>
   </si>
   <si>
     <t>Our European Ingredients | NZMP.com</t>
@@ -340,13 +340,13 @@
     <t>global/en/about-nzmp/global-ingredients/our-global-ingredients.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-category","cards-category","cards-value","cards-value","cards-value","cards-value"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","cards-category","cards-category","cards-value","cards-value","cards-value","cards-value"]</t>
   </si>
   <si>
     <t>global/en/about-nzmp/global-ingredients/our-global-ingredients</t>
   </si>
   <si>
-    <t>2026-08-13T23:46:09.109Z</t>
+    <t>2026-08-14T01:58:48.269Z</t>
   </si>
   <si>
     <t>Our Global Ingredients | NZMP.com</t>
@@ -361,7 +361,7 @@
     <t>global/en/about-nzmp/global-ingredients/our-new-zealand-ingredients</t>
   </si>
   <si>
-    <t>2026-08-13T23:46:18.260Z</t>
+    <t>2026-08-14T01:58:57.736Z</t>
   </si>
   <si>
     <t>Our New Zealand Ingredients | NZMP.com</t>
@@ -376,7 +376,7 @@
     <t>global/en/about-nzmp/global-ingredients/our-north-american-ingredients</t>
   </si>
   <si>
-    <t>2026-08-13T23:46:24.482Z</t>
+    <t>2026-08-14T01:59:05.725Z</t>
   </si>
   <si>
     <t>Our North American Ingredients | NZMP.com</t>
@@ -388,13 +388,13 @@
     <t>global/en/applications/organic-dairy/organic-product-claims.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-value","cards-value"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","cards-value","cards-value"]</t>
   </si>
   <si>
     <t>global/en/applications/organic-dairy/organic-product-claims</t>
   </si>
   <si>
-    <t>2026-08-13T23:47:47.471Z</t>
+    <t>2026-08-14T02:00:35.759Z</t>
   </si>
   <si>
     <t>Organic Product Claims | NZMP.com</t>
@@ -406,13 +406,13 @@
     <t>global/en/applications/organic-dairy/organic-supply.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","cards-value"]</t>
   </si>
   <si>
     <t>global/en/applications/organic-dairy/organic-supply</t>
   </si>
   <si>
-    <t>2026-08-13T23:47:54.925Z</t>
+    <t>2026-08-14T02:00:42.923Z</t>
   </si>
   <si>
     <t>Organic Supply | NZMP.com</t>
@@ -424,13 +424,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature"]</t>
+    <t>["columns-banner","columns-feature","columns-feature"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T23:48:24.667Z</t>
+    <t>2026-08-14T02:01:15.122Z</t>
   </si>
   <si>
     <t>Cheddar Cheese - Ingredients &amp; Products | NZMP.com</t>
@@ -442,13 +442,13 @@
     <t>global/en/ingredients/cheese/cream-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature"]</t>
+    <t>["columns-banner","columns-feature"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cream-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T23:48:35.558Z</t>
+    <t>2026-08-14T02:01:25.681Z</t>
   </si>
   <si>
     <t>Cream Cheese - Ingredients &amp; Products | NZMP.com</t>
@@ -460,13 +460,13 @@
     <t>global/en/ingredients/cheese/mozzarella-options.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","cards-value","cards-value"]</t>
+    <t>["columns-banner","columns-feature","cards-value","cards-value"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/mozzarella-options</t>
   </si>
   <si>
-    <t>2026-08-13T23:48:44.089Z</t>
+    <t>2026-08-14T02:01:35.759Z</t>
   </si>
   <si>
     <t>Mozzarella Cheese - Ingredients &amp; Products | NZMP.com</t>
@@ -478,13 +478,13 @@
     <t>global/en/ingredients/cheese/new-zealand-cheeses.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner"]</t>
+    <t>["columns-banner"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/new-zealand-cheeses</t>
   </si>
   <si>
-    <t>2026-08-13T23:48:57.621Z</t>
+    <t>2026-08-14T02:01:52.659Z</t>
   </si>
   <si>
     <t>Uniquely from New Zealand Cheese - Ingredients &amp; Products | NZMP.com</t>
@@ -499,7 +499,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:04.959Z</t>
+    <t>2026-08-14T02:02:00.713Z</t>
   </si>
   <si>
     <t>Parmesan and Popular cheeses | NZMP.com</t>
@@ -511,13 +511,13 @@
     <t>global/en/ingredients/cheese/repack-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/repack-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:11.863Z</t>
+    <t>2026-08-14T02:02:10.061Z</t>
   </si>
   <si>
     <t>Repack Cheese - Ingredients &amp; Products | NZMP.com</t>
@@ -529,13 +529,13 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-value","cards-value"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","cards-value","cards-value"]</t>
   </si>
   <si>
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:20.764Z</t>
+    <t>2026-08-14T02:02:20.727Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat | NZMP.com</t>
@@ -550,7 +550,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:27.460Z</t>
+    <t>2026-08-14T02:02:28.117Z</t>
   </si>
   <si>
     <t>Butter - Ingredients &amp; Products | NZMP.com</t>
@@ -565,7 +565,7 @@
     <t>global/en/ingredients/dairy-fats-cream/cream-powder</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:34.663Z</t>
+    <t>2026-08-14T02:02:36.506Z</t>
   </si>
   <si>
     <t>Cream Powder - Dairy Fats Ingredients | NZMP.com</t>
@@ -580,7 +580,7 @@
     <t>global/en/ingredients/dairy-fats-cream/repack-butter</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:41.822Z</t>
+    <t>2026-08-14T02:02:44.625Z</t>
   </si>
   <si>
     <t>Repack Butter - Ingredients &amp; Products | NZMP.com</t>
@@ -592,13 +592,13 @@
     <t>global/en/ingredients/dairy-fats-cream/uht-cream.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-category"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","cards-category"]</t>
   </si>
   <si>
     <t>global/en/ingredients/dairy-fats-cream/uht-cream</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:47.598Z</t>
+    <t>2026-08-14T02:02:51.592Z</t>
   </si>
   <si>
     <t>UHT Cream | NZMP.com</t>
@@ -610,13 +610,13 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T23:49:54.464Z</t>
+    <t>2026-08-14T02:02:59.759Z</t>
   </si>
   <si>
     <t>Buttermilk Powder - Ingredients &amp; Products | NZMP.com</t>
@@ -628,13 +628,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:02.024Z</t>
+    <t>2026-08-14T02:03:09.220Z</t>
   </si>
   <si>
     <t>Instant Milk Powder - Ingredients &amp; Products | NZMP.com</t>
@@ -649,7 +649,7 @@
     <t>global/en/ingredients/powders-concentrates/lactose</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:08.323Z</t>
+    <t>2026-08-14T02:03:17.323Z</t>
   </si>
   <si>
     <t>Lactose - Ingredients &amp; Products | NZMP.com</t>
@@ -661,7 +661,7 @@
     <t>global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate</t>
@@ -670,7 +670,7 @@
     <t>ingredient-product-detail</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:25.188Z</t>
+    <t>2026-08-14T01:44:33.033Z</t>
   </si>
   <si>
     <t>Frozen Whole Milk Concentrate | NZMP.com</t>
@@ -682,13 +682,13 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:13.822Z</t>
+    <t>2026-08-14T02:03:24.323Z</t>
   </si>
   <si>
     <t>Paediatric Grade Powders | NZMP.com</t>
@@ -703,7 +703,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:21.160Z</t>
+    <t>2026-08-14T02:03:33.123Z</t>
   </si>
   <si>
     <t>Skim Milk Powder - Ingredients &amp; Products | NZMP.com</t>
@@ -718,7 +718,7 @@
     <t>global/en/ingredients/powders-concentrates/whey-powder</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:28.059Z</t>
+    <t>2026-08-14T02:03:40.168Z</t>
   </si>
   <si>
     <t>Whey Powder - Ingredients &amp; Products | NZMP.com</t>
@@ -733,7 +733,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:36.482Z</t>
+    <t>2026-08-14T02:03:47.263Z</t>
   </si>
   <si>
     <t>Whole Milk Powder | NZMP.com</t>
@@ -748,7 +748,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:43.522Z</t>
+    <t>2026-08-14T02:03:54.267Z</t>
   </si>
   <si>
     <t>Caseins and Caseinates | NZMP.com</t>
@@ -763,7 +763,7 @@
     <t>global/en/ingredients/proteins/functional-proteins</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:58.239Z</t>
+    <t>2026-08-14T02:04:11.393Z</t>
   </si>
   <si>
     <t>Functional Proteins - Ingredients &amp; Products | NZMP.com</t>
@@ -775,13 +775,13 @@
     <t>global/en/ingredients/proteins/hydrolysates.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:04.924Z</t>
+    <t>2026-08-14T02:04:19.923Z</t>
   </si>
   <si>
     <t>Hydrolysates - Ingredients &amp; Products | NZMP.com</t>
@@ -796,7 +796,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:13.056Z</t>
+    <t>2026-08-14T02:04:27.741Z</t>
   </si>
   <si>
     <t>Milk Protein Concentrates - Proteins | NZMP.com</t>
@@ -811,7 +811,7 @@
     <t>global/en/ingredients/proteins/nzmp-dpc</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:10.880Z</t>
+    <t>2026-08-14T02:05:31.615Z</t>
   </si>
   <si>
     <t>NZMP CrispBar Dairy Protein Crisp | NZMP.com</t>
@@ -826,7 +826,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:18.624Z</t>
+    <t>2026-08-14T02:05:39.217Z</t>
   </si>
   <si>
     <t>Whey Protein Concentrates | NZMP.com</t>
@@ -841,7 +841,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:48.058Z</t>
+    <t>2026-08-14T02:06:13.885Z</t>
   </si>
   <si>
     <t>Whey Protein Isolates | NZMP.com</t>
@@ -856,7 +856,7 @@
     <t>global/en/ingredients/specialty/complex-lipids</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:01.158Z</t>
+    <t>2026-08-14T02:06:29.959Z</t>
   </si>
   <si>
     <t>MFGM Complex Lipids | NZMP.com</t>
@@ -871,7 +871,7 @@
     <t>global/en/ingredients/specialty/hydrolysates</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:08.624Z</t>
+    <t>2026-08-14T02:06:36.490Z</t>
   </si>
   <si>
     <t>Hydrolysates - Specialty Ingredients | NZMP.com</t>
@@ -883,13 +883,13 @@
     <t>global/en/ingredients/specialty/lactoferrin.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
   </si>
   <si>
     <t>global/en/ingredients/specialty/lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:29.630Z</t>
+    <t>2026-08-14T02:07:03.459Z</t>
   </si>
   <si>
     <t>Lactoferrin - Speciality Ingredients | NZMP.com</t>
@@ -904,7 +904,7 @@
     <t>global/en/ingredients/specialty/lactose</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:37.970Z</t>
+    <t>2026-08-14T02:07:11.601Z</t>
   </si>
   <si>
     <t>Lactose - Speciality Ingredients | NZMP.com</t>
@@ -919,7 +919,7 @@
     <t>global/en/ingredients/specialty/prebiotics</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:45.151Z</t>
+    <t>2026-08-14T02:07:20.460Z</t>
   </si>
   <si>
     <t>Prebiotics - Speciality Ingredients | NZMP.com</t>
@@ -931,13 +931,13 @@
     <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-teaser"]</t>
+    <t>["columns-banner","columns-feature","cards-category","cards-teaser"]</t>
   </si>
   <si>
     <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:12.757Z</t>
+    <t>2026-08-14T02:07:51.063Z</t>
   </si>
   <si>
     <t>World-Leading Global Dairy Expertise | NZMP.com</t>
@@ -949,13 +949,13 @@
     <t>global/en/solutions/innovation-and-ingenuity/our-protein-expertise.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","cards-value","cards-value","cards-value","cards-value","cards-value"]</t>
+    <t>["columns-banner","columns-feature","cards-value","cards-value","cards-value","cards-value","cards-value"]</t>
   </si>
   <si>
     <t>global/en/solutions/innovation-and-ingenuity/our-protein-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T23:55:04.443Z</t>
+    <t>2026-08-14T02:08:40.070Z</t>
   </si>
   <si>
     <t>Our Protein Expertise - Innovation &amp; Expertise | NZMP.com</t>
@@ -970,7 +970,7 @@
     <t>global/en/solutions/innovation-and-ingenuity/the-fonterra-research-and-development-centre</t>
   </si>
   <si>
-    <t>2026-08-13T23:55:12.107Z</t>
+    <t>2026-08-14T02:08:48.553Z</t>
   </si>
   <si>
     <t>The Fonterra Research and Development Centre | NZMP.com</t>
@@ -982,13 +982,13 @@
     <t>global/en/solutions/third-party-manufacturing/private-label-solutions.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
+    <t>["columns-banner","columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
   </si>
   <si>
     <t>global/en/solutions/third-party-manufacturing/private-label-solutions</t>
   </si>
   <si>
-    <t>2026-08-13T23:55:35.658Z</t>
+    <t>2026-08-14T02:09:09.627Z</t>
   </si>
   <si>
     <t>Our Private Label Solutions | NZMP.com</t>
@@ -1000,13 +1000,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:15.215Z</t>
+    <t>2026-08-14T01:35:22.896Z</t>
   </si>
   <si>
     <t>Cheddar Cheese (Australia Specification) | NZMP Dairy Ingredients | NZMP.com</t>
@@ -1018,13 +1018,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:23.694Z</t>
+    <t>2026-08-14T01:36:15.923Z</t>
   </si>
   <si>
     <t>Cheddar Cheese Frozen | NZMP.com</t>
@@ -1039,7 +1039,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:33.759Z</t>
+    <t>2026-08-14T01:36:24.161Z</t>
   </si>
   <si>
     <t>Cheddar Cheese for Manufacturing | NZMP.com</t>
@@ -1051,13 +1051,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:40.959Z</t>
+    <t>2026-08-14T01:36:32.024Z</t>
   </si>
   <si>
     <t>Cheddar Cheese | NZMP Dairy Ingredients | NZMP.com</t>
@@ -1069,13 +1069,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:49.141Z</t>
+    <t>2026-08-14T01:36:40.029Z</t>
   </si>
   <si>
     <t>Coloured Cheddar Cheese | NZMP.com</t>
@@ -1087,13 +1087,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:56.362Z</t>
+    <t>2026-08-14T01:36:47.626Z</t>
   </si>
   <si>
     <t>Frozen Functional Cheddar Cheese | NZMP.com</t>
@@ -1105,13 +1105,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:04.559Z</t>
+    <t>2026-08-14T01:36:54.630Z</t>
   </si>
   <si>
     <t>Mature Cheddar | NZMP.com</t>
@@ -1126,7 +1126,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:13.023Z</t>
+    <t>2026-08-14T01:37:02.427Z</t>
   </si>
   <si>
     <t>Organic Frozen Cheddar Cheese, Reduced Salt  | NZMP.com</t>
@@ -1138,13 +1138,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:20.559Z</t>
+    <t>2026-08-14T01:37:10.659Z</t>
   </si>
   <si>
     <t>Organic Mature Cheddar Cheese | NZMP.com</t>
@@ -1159,7 +1159,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:30.171Z</t>
+    <t>2026-08-14T01:37:20.257Z</t>
   </si>
   <si>
     <t>Organic Mild Cheddar Cheese | NZMP.com</t>
@@ -1171,13 +1171,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:39.195Z</t>
+    <t>2026-08-14T01:37:28.686Z</t>
   </si>
   <si>
     <t>Strong Cheddar Cheese for Manufacturing | NZMP.com</t>
@@ -1192,7 +1192,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:46.723Z</t>
+    <t>2026-08-14T01:37:35.638Z</t>
   </si>
   <si>
     <t>Young Cheddar Cheese for Manufacturing GDT Specification | NZMP.com</t>
@@ -1207,7 +1207,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:55.022Z</t>
+    <t>2026-08-14T01:37:44.937Z</t>
   </si>
   <si>
     <t>Easy Shred Mozzarella | NZMP.com</t>
@@ -1222,7 +1222,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/european-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T23:48:51.698Z</t>
+    <t>2026-08-14T02:01:45.220Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/european-mozzarella.html</t>
@@ -1234,7 +1234,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:04.860Z</t>
+    <t>2026-08-14T01:37:54.322Z</t>
   </si>
   <si>
     <t>Frozen Mozzarella | NZMP.com</t>
@@ -1249,7 +1249,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:13.085Z</t>
+    <t>2026-08-14T01:38:04.836Z</t>
   </si>
   <si>
     <t>Individually Quick Frozen Mozzarella | NZMP.com</t>
@@ -1264,7 +1264,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:22.024Z</t>
+    <t>2026-08-14T01:38:13.261Z</t>
   </si>
   <si>
     <t>Lower Salt Mozzarella | NZMP.com</t>
@@ -1279,7 +1279,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:32.323Z</t>
+    <t>2026-08-14T01:38:21.948Z</t>
   </si>
   <si>
     <t>Medium Fat Mozzarella | NZMP.com</t>
@@ -1294,7 +1294,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-curd</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:39.974Z</t>
+    <t>2026-08-14T01:38:29.639Z</t>
   </si>
   <si>
     <t>Mozzarella Curd | NZMP.com</t>
@@ -1306,13 +1306,13 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:49.166Z</t>
+    <t>2026-08-14T01:38:39.928Z</t>
   </si>
   <si>
     <t>Premium Mozzarella Frozen (Made in Australia) | NZMP.com</t>
@@ -1327,7 +1327,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-nz</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:58.334Z</t>
+    <t>2026-08-14T01:38:49.223Z</t>
   </si>
   <si>
     <t>Premium Mozzarella Frozen (Made in New Zealand) | NZMP.com</t>
@@ -1342,7 +1342,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/premium-chilled-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:08.123Z</t>
+    <t>2026-08-14T01:38:57.588Z</t>
   </si>
   <si>
     <t>Premium Chilled Mozzarella | NZMP.com</t>
@@ -1357,7 +1357,7 @@
     <t>global/en/ingredients/cheese/new-zealand-cheeses/egmont-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:15.122Z</t>
+    <t>2026-08-14T01:39:05.359Z</t>
   </si>
   <si>
     <t>Egmont™ Cheese | NZMP.com</t>
@@ -1372,7 +1372,7 @@
     <t>global/en/ingredients/cheese/new-zealand-cheeses/noble-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:23.064Z</t>
+    <t>2026-08-14T01:39:12.825Z</t>
   </si>
   <si>
     <t>Noble™ Cheese | NZMP.com</t>
@@ -1384,13 +1384,13 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/colby-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/colby-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:30.160Z</t>
+    <t>2026-08-14T01:39:18.624Z</t>
   </si>
   <si>
     <t>Colby Cheese | NZMP.com</t>
@@ -1405,7 +1405,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/edam-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:38.122Z</t>
+    <t>2026-08-14T01:39:25.564Z</t>
   </si>
   <si>
     <t>Edam Cheese | NZMP.com</t>
@@ -1420,7 +1420,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/gouda-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:46.093Z</t>
+    <t>2026-08-14T01:39:32.499Z</t>
   </si>
   <si>
     <t>Gouda Cheese - NZMP Dairy Ingredients | NZMP.com</t>
@@ -1435,7 +1435,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/parmesan-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:53.223Z</t>
+    <t>2026-08-14T01:39:38.760Z</t>
   </si>
   <si>
     <t>Parmesan | NZMP.com</t>
@@ -1450,7 +1450,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/swiss-style-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:00.222Z</t>
+    <t>2026-08-14T01:39:45.410Z</t>
   </si>
   <si>
     <t>Swiss-Style Cheese | NZMP.com</t>
@@ -1465,7 +1465,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-15l-convenience-pack</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:09.445Z</t>
+    <t>2026-08-14T01:39:55.173Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat 15L/13.5KG Convenience Pack | NZMP.com</t>
@@ -1480,7 +1480,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-premium-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:17.380Z</t>
+    <t>2026-08-14T01:40:03.077Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Premium Grade GDT Specification | NZMP.com</t>
@@ -1495,7 +1495,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-premium</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:24.337Z</t>
+    <t>2026-08-14T01:40:10.722Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Premium Grade | NZMP.com</t>
@@ -1510,7 +1510,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-regular-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:32.037Z</t>
+    <t>2026-08-14T01:40:18.535Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Regular Grade GDT Specification | NZMP.com</t>
@@ -1525,7 +1525,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-regular</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:40.884Z</t>
+    <t>2026-08-14T01:40:27.112Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Regular Grade | NZMP.com</t>
@@ -1540,7 +1540,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/organic-anhydrous-milk-fat-premium</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:48.228Z</t>
+    <t>2026-08-14T01:40:34.204Z</t>
   </si>
   <si>
     <t>Organic Anhydrous Milk Fat Premium Grade | NZMP.com</t>
@@ -1555,7 +1555,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/lactic-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:57.225Z</t>
+    <t>2026-08-14T01:40:42.939Z</t>
   </si>
   <si>
     <t>Lactic Butter | NZMP.com</t>
@@ -1570,7 +1570,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-salted-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:05.757Z</t>
+    <t>2026-08-14T01:40:50.896Z</t>
   </si>
   <si>
     <t>Organic Salted Butter | NZMP.com</t>
@@ -1585,7 +1585,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-unsalted-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:13.771Z</t>
+    <t>2026-08-14T01:40:57.923Z</t>
   </si>
   <si>
     <t>Organic Unsalted Butter | NZMP.com</t>
@@ -1600,7 +1600,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-unsalted-lactic-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:23.223Z</t>
+    <t>2026-08-14T01:41:05.494Z</t>
   </si>
   <si>
     <t>Organic Lactic Unsalted Butter | NZMP.com</t>
@@ -1615,7 +1615,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/salted-creamery-butter-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:30.596Z</t>
+    <t>2026-08-14T01:41:12.323Z</t>
   </si>
   <si>
     <t>Salted Creamery Butter GDT Specification | NZMP.com</t>
@@ -1630,7 +1630,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/salted-creamery-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:38.728Z</t>
+    <t>2026-08-14T01:41:18.846Z</t>
   </si>
   <si>
     <t>Salted Creamery Butter | NZMP.com</t>
@@ -1642,13 +1642,13 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-butter-convenience-pack.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-butter-convenience-pack</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:46.860Z</t>
+    <t>2026-08-14T01:41:29.060Z</t>
   </si>
   <si>
     <t>NZMP™ Unsalted Butter, 12.5kg Convenience Pack | NZMP.com</t>
@@ -1663,7 +1663,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-creamery-butter-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:55.505Z</t>
+    <t>2026-08-14T01:41:36.846Z</t>
   </si>
   <si>
     <t>Unsalted Creamery Butter GDT Specification | NZMP.com</t>
@@ -1678,7 +1678,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-creamery-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:21:49.560Z</t>
+    <t>2026-08-14T01:41:44.843Z</t>
   </si>
   <si>
     <t>Unsalted Creamery Butter | NZMP.com</t>
@@ -1693,7 +1693,7 @@
     <t>global/en/ingredients/dairy-fats-cream/cream-cheese/cream-cheese-traditional</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:03.353Z</t>
+    <t>2026-08-14T01:41:53.585Z</t>
   </si>
   <si>
     <t>Cream Cheese Traditional | NZMP.com</t>
@@ -1708,7 +1708,7 @@
     <t>global/en/ingredients/dairy-fats-cream/cream-powder/cream-powder-55</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:12.161Z</t>
+    <t>2026-08-14T01:42:02.959Z</t>
   </si>
   <si>
     <t>Cream Powder 55 | NZMP.com</t>
@@ -1723,7 +1723,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:20.527Z</t>
+    <t>2026-08-14T01:42:12.034Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder (Australia Specification) | NZMP.com</t>
@@ -1738,7 +1738,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder-uht-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:26.857Z</t>
+    <t>2026-08-14T01:42:21.925Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder for UHT Milk GDT Specification | NZMP.com</t>
@@ -1753,7 +1753,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:36.708Z</t>
+    <t>2026-08-14T01:42:42.268Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder | NZMP.com</t>
@@ -1768,7 +1768,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder-for-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:45.947Z</t>
+    <t>2026-08-14T01:42:49.477Z</t>
   </si>
   <si>
     <t>Fat Filled Milk Powder for Yoghurt | NZMP.com</t>
@@ -1780,13 +1780,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:54.960Z</t>
+    <t>2026-08-14T01:42:58.923Z</t>
   </si>
   <si>
     <t>Fat Filled Milk Powder Instant Fortified | NZMP.com</t>
@@ -1798,13 +1798,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/gold-instant-whole-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/gold-instant-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:03.328Z</t>
+    <t>2026-08-14T01:43:07.035Z</t>
   </si>
   <si>
     <t>Gold Instant Whole Milk Powder | NZMP.com</t>
@@ -1819,7 +1819,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/instant-skim-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:11.088Z</t>
+    <t>2026-08-14T01:43:15.723Z</t>
   </si>
   <si>
     <t>Instant Skim Milk Powder | NZMP.com</t>
@@ -1834,7 +1834,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/instant-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:18.924Z</t>
+    <t>2026-08-14T01:43:24.557Z</t>
   </si>
   <si>
     <t>Instant Whole Milk Powder | NZMP Ingredients | NZMP.com</t>
@@ -1849,7 +1849,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-fortified-plus-instant-wmp</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:26.321Z</t>
+    <t>2026-08-14T01:43:31.943Z</t>
   </si>
   <si>
     <t>Fortified+ Instant Whole Milk Powder | NZMP.com</t>
@@ -1864,7 +1864,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-gold-instant-wmp</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:35.123Z</t>
+    <t>2026-08-14T01:43:41.630Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-gold-instant-wmp.html</t>
@@ -1873,13 +1873,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-low-cost-pure-instant-dairy-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-low-cost-pure-instant-dairy-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:43.175Z</t>
+    <t>2026-08-14T01:43:49.641Z</t>
   </si>
   <si>
     <t>Low-Cost Pure Instant Dairy Powder | NZMP.com</t>
@@ -1891,13 +1891,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-nutriwhite-dairy-based-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-nutriwhite-dairy-based-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:52.280Z</t>
+    <t>2026-08-14T01:43:58.900Z</t>
   </si>
   <si>
     <t>NutriWhite Dairy-Based Powder | NZMP Dairy Ingredients | NZMP.com</t>
@@ -1909,13 +1909,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-protein-plus-instant-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-protein-plus-instant-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:01.245Z</t>
+    <t>2026-08-14T01:44:08.425Z</t>
   </si>
   <si>
     <t>Protein+ Instant Milk Powder | NZMP.com</t>
@@ -1930,7 +1930,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/super-fortified-instant-smp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:10.156Z</t>
+    <t>2026-08-14T01:44:16.966Z</t>
   </si>
   <si>
     <t>Super Fortified Instant Skim Milk Powder | NZMP.com</t>
@@ -1945,7 +1945,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/whole-milk-powder-instant-fortified</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:18.198Z</t>
+    <t>2026-08-14T01:44:25.490Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder Instant Fortified with Vitamins A &amp; D | NZMP.com</t>
@@ -1957,13 +1957,13 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-demineralised-whey-powder-90.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","carousel-news"]</t>
+    <t>["columns-product","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-demineralised-whey-powder-90</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:31.261Z</t>
+    <t>2026-08-14T01:44:39.094Z</t>
   </si>
   <si>
     <t>SureStart™ Demineralised Whey Powder 90% | NZMP.com</t>
@@ -1978,7 +1978,7 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-regular-skim-milk-powder-wetapp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:39.058Z</t>
+    <t>2026-08-14T01:44:47.024Z</t>
   </si>
   <si>
     <t>Paediatric Grade Regular Skim Milk Powder | NZMP.com</t>
@@ -1993,7 +1993,7 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-regular-whole-milk-powder-wetapp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:46.289Z</t>
+    <t>2026-08-14T01:44:53.565Z</t>
   </si>
   <si>
     <t>Paediatric Grade Regular Whole Milk Powder | NZMP.com</t>
@@ -2008,7 +2008,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/organic-skim-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:54.988Z</t>
+    <t>2026-08-14T01:45:01.460Z</t>
   </si>
   <si>
     <t>Organic Skim Milk Powder | NZMP.com</t>
@@ -2023,7 +2023,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-high-heat-hs-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:03.060Z</t>
+    <t>2026-08-14T01:45:09.737Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder High Heat Heat Stable GDT Specification | NZMP.com</t>
@@ -2038,7 +2038,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-high-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:12.820Z</t>
+    <t>2026-08-14T01:45:17.860Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder High Heat | NZMP.com</t>
@@ -2053,7 +2053,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-low-heat-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:20.420Z</t>
+    <t>2026-08-14T01:45:24.376Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Low Heat GDT Specification | NZMP.com</t>
@@ -2068,7 +2068,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-low-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:14.609Z</t>
+    <t>2026-08-14T01:46:18.662Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Low Heat | NZMP.com</t>
@@ -2080,13 +2080,13 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:24.471Z</t>
+    <t>2026-08-14T01:46:26.637Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat (Australia Specification) | NZMP.com</t>
@@ -2101,7 +2101,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:32.036Z</t>
+    <t>2026-08-14T01:46:34.088Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat GDT Specification | NZMP.com</t>
@@ -2116,7 +2116,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:40.541Z</t>
+    <t>2026-08-14T01:46:43.360Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat | NZMP.com</t>
@@ -2131,7 +2131,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-uht-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:47.775Z</t>
+    <t>2026-08-14T01:46:51.521Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder for UHT Milk GDT Specification | NZMP.com</t>
@@ -2146,7 +2146,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:55.557Z</t>
+    <t>2026-08-14T01:47:00.675Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder for UHT Milk | NZMP.com</t>
@@ -2161,7 +2161,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/smp-for-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:02.437Z</t>
+    <t>2026-08-14T01:47:07.992Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder/smp-for-uht.html</t>
@@ -2173,7 +2173,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/super-fortified-instant-smp</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:11.234Z</t>
+    <t>2026-08-14T01:47:16.484Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder/super-fortified-instant-smp.html</t>
@@ -2185,7 +2185,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/surestart-regular-smp-low-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:19.248Z</t>
+    <t>2026-08-14T01:47:23.983Z</t>
   </si>
   <si>
     <t>SureStart™ Regular Skim Milk Powder Low Heat | NZMP Ingredients | NZMP.com</t>
@@ -2200,7 +2200,7 @@
     <t>global/en/ingredients/powders-concentrates/whey-powder/nzmp-whey-powder-621</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:27.257Z</t>
+    <t>2026-08-14T01:47:33.421Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Powder 621 | NZMP.com</t>
@@ -2215,7 +2215,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/organic-regular-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:35.578Z</t>
+    <t>2026-08-14T01:47:41.419Z</t>
   </si>
   <si>
     <t>Organic Whole Milk Powder | NZMP.com</t>
@@ -2230,7 +2230,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:43.681Z</t>
+    <t>2026-08-14T01:47:50.696Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder GDT Specification | NZMP.com</t>
@@ -2245,7 +2245,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-high-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:51.758Z</t>
+    <t>2026-08-14T01:48:00.589Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder High Heat | NZMP.com</t>
@@ -2260,7 +2260,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-repack</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:58.959Z</t>
+    <t>2026-08-14T01:48:07.619Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Repack | NZMP.com</t>
@@ -2275,7 +2275,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-uht-28-fat</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:07.505Z</t>
+    <t>2026-08-14T01:48:16.238Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder 28% Fat for UHT | NZMP.com</t>
@@ -2290,7 +2290,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:16.195Z</t>
+    <t>2026-08-14T01:48:24.659Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for UHT Milk | NZMP.com</t>
@@ -2305,7 +2305,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:25.141Z</t>
+    <t>2026-08-14T01:48:32.240Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder | NZMP.com</t>
@@ -2320,7 +2320,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-blending</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:32.225Z</t>
+    <t>2026-08-14T01:48:40.406Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Blending | NZMP.com</t>
@@ -2335,7 +2335,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-tea</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:40.528Z</t>
+    <t>2026-08-14T01:48:48.410Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Tea | NZMP.com</t>
@@ -2347,13 +2347,13 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-yoghurt.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:48.780Z</t>
+    <t>2026-08-14T01:48:56.432Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Yoghurt | NZMP.com</t>
@@ -2368,7 +2368,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/whole-milk-powder-recombined-evaporated-milk</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:55.898Z</t>
+    <t>2026-08-14T01:49:05.260Z</t>
   </si>
   <si>
     <t>Whole Milk Powder for Recombined Evaporated Milk | NZMP.com</t>
@@ -2383,7 +2383,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/wmp-uht-perform</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:03.666Z</t>
+    <t>2026-08-14T01:49:12.961Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder UHT Perform - NZMP Ingredients | NZMP.com</t>
@@ -2395,13 +2395,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-7051.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-7051</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:31.160Z</t>
+    <t>2026-08-14T01:50:39.923Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 7051 | NZMP.com</t>
@@ -2413,13 +2413,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-821.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-821</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:39.060Z</t>
+    <t>2026-08-14T01:50:48.060Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 821 | NZMP.com</t>
@@ -2431,13 +2431,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-917.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-917</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:46.974Z</t>
+    <t>2026-08-14T01:50:56.661Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 917 | NZMP.com</t>
@@ -2449,13 +2449,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-470.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-470</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:54.400Z</t>
+    <t>2026-08-14T01:51:03.920Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 470 | NZMP.com</t>
@@ -2467,13 +2467,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:04.397Z</t>
+    <t>2026-08-14T01:51:14.071Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 485 | NZMP.com</t>
@@ -2488,7 +2488,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:20.860Z</t>
+    <t>2026-08-14T02:04:36.008Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt.html</t>
@@ -2500,7 +2500,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:29.757Z</t>
+    <t>2026-08-14T02:04:44.123Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt.html</t>
@@ -2512,7 +2512,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4851</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:14.149Z</t>
+    <t>2026-08-14T01:51:23.683Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4851 | NZMP.com</t>
@@ -2527,7 +2527,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:35.757Z</t>
+    <t>2026-08-14T02:04:51.974Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt.html</t>
@@ -2539,7 +2539,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:23.524Z</t>
+    <t>2026-08-14T01:51:33.624Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4861 | NZMP.com</t>
@@ -2554,7 +2554,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:43.260Z</t>
+    <t>2026-08-14T02:05:00.780Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt.html</t>
@@ -2566,7 +2566,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:49.341Z</t>
+    <t>2026-08-14T02:05:08.359Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867.html</t>
@@ -2578,7 +2578,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T23:51:56.622Z</t>
+    <t>2026-08-14T02:05:16.867Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt.html</t>
@@ -2587,13 +2587,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:35.766Z</t>
+    <t>2026-08-14T01:51:45.230Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4882 | NZMP.com</t>
@@ -2608,7 +2608,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4887</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:46.378Z</t>
+    <t>2026-08-14T01:51:54.159Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4887 | NZMP.com</t>
@@ -2623,7 +2623,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:04.924Z</t>
+    <t>2026-08-14T02:05:23.771Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857.html</t>
@@ -2635,7 +2635,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-sureprotein-mpc-4881</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:55.459Z</t>
+    <t>2026-08-14T01:52:04.114Z</t>
   </si>
   <si>
     <t>SureProtein™ Milk Protein Concentrate 4881 | NZMP.com</t>
@@ -2650,7 +2650,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/organic-milk-protein-concentrate-485</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:03.223Z</t>
+    <t>2026-08-14T01:52:13.022Z</t>
   </si>
   <si>
     <t>Organic Milk Protein Concentrate (Regular 85%) | NZMP.com</t>
@@ -2665,7 +2665,7 @@
     <t>global/en/ingredients/proteins/milk-protein-isolates/nzmp-milk-protein-isolate-4900</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:11.864Z</t>
+    <t>2026-08-14T01:52:21.729Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Isolate 4900 | NZMP.com</t>
@@ -2680,7 +2680,7 @@
     <t>global/en/ingredients/proteins/milk-protein-isolates/nzmp-softbar-1000</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:19.837Z</t>
+    <t>2026-08-14T01:52:29.172Z</t>
   </si>
   <si>
     <t>SureProtein™ Milk Protein Isolate SoftBar 1000 | NZMP.com</t>
@@ -2695,7 +2695,7 @@
     <t>global/en/ingredients/proteins/total-milk-proteins/nzmp-total-milk-protein-shortbar-1104</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:27.023Z</t>
+    <t>2026-08-14T01:52:37.097Z</t>
   </si>
   <si>
     <t>SureProtein™ Total Milk Protein ShortBar 1104 | NZMP.com</t>
@@ -2710,7 +2710,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-bioactive-whey-protein</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:36.202Z</t>
+    <t>2026-08-14T01:52:45.939Z</t>
   </si>
   <si>
     <t>Bioactive Whey Protein | NZMP.com</t>
@@ -2725,7 +2725,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-dairy-protein-crisps-crispbar</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:43.023Z</t>
+    <t>2026-08-14T01:52:54.158Z</t>
   </si>
   <si>
     <t>NZMP™ Dairy Protein Crisps 600 | NZMP.com</t>
@@ -2740,7 +2740,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flex-wpc-515</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:50.124Z</t>
+    <t>2026-08-14T01:53:01.874Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 515 | NZMP.com</t>
@@ -2755,7 +2755,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:26.525Z</t>
+    <t>2026-08-14T02:05:48.423Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar.html</t>
@@ -2767,7 +2767,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flow-wpc-510</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:58.520Z</t>
+    <t>2026-08-14T01:53:08.822Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 510 | NZMP.com</t>
@@ -2782,7 +2782,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-instant-whey-protein-concentrate-450</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:05.241Z</t>
+    <t>2026-08-14T01:53:16.060Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Concentrate 450 | NZMP.com</t>
@@ -2797,7 +2797,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-pro-optima-wpc-567</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:14.959Z</t>
+    <t>2026-08-14T01:53:26.564Z</t>
   </si>
   <si>
     <t>NZMP™ Pro-Optima™ Whey Protein Concentrate | NZMP.com</t>
@@ -2812,7 +2812,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:34.460Z</t>
+    <t>2026-08-14T02:05:56.640Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392.html</t>
@@ -2821,13 +2821,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-132.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-132</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:23.568Z</t>
+    <t>2026-08-14T01:53:33.622Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 132 | NZMP.com</t>
@@ -2842,7 +2842,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-162</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:31.064Z</t>
+    <t>2026-08-14T01:53:41.522Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 162 | NZMP.com</t>
@@ -2857,7 +2857,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-322</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:38.541Z</t>
+    <t>2026-08-14T01:53:49.958Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 322 | NZMP.com</t>
@@ -2869,13 +2869,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-352.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-352</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:46.260Z</t>
+    <t>2026-08-14T01:53:58.804Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 352 | NZMP.com</t>
@@ -2890,7 +2890,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-356</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:55.126Z</t>
+    <t>2026-08-14T01:54:07.224Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 356 | NZMP.com</t>
@@ -2905,7 +2905,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-392</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:03.101Z</t>
+    <t>2026-08-14T01:54:15.790Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 392 | NZMP.com</t>
@@ -2920,7 +2920,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-397</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:12.338Z</t>
+    <t>2026-08-14T01:54:23.819Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 397 | NZMP.com</t>
@@ -2935,7 +2935,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-457-decolorized</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:20.137Z</t>
+    <t>2026-08-14T01:54:33.675Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 457 | NZMP.com</t>
@@ -2950,7 +2950,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-472</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:29.223Z</t>
+    <t>2026-08-14T01:54:42.974Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 472 | NZMP.com</t>
@@ -2965,7 +2965,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-480-instantised</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:36.615Z</t>
+    <t>2026-08-14T01:54:50.322Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Concentrate 480 | NZMP.com</t>
@@ -2980,7 +2980,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-7009</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:44.423Z</t>
+    <t>2026-08-14T01:54:58.322Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 7009 | NZMP.com</t>
@@ -2992,13 +2992,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:52.271Z</t>
+    <t>2026-08-14T01:55:07.591Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 550 | NZMP.com</t>
@@ -3013,7 +3013,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:41.460Z</t>
+    <t>2026-08-14T02:06:05.724Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt.html</t>
@@ -3025,7 +3025,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/organic-whey-protein-concentrate-392</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:00.210Z</t>
+    <t>2026-08-14T01:55:15.558Z</t>
   </si>
   <si>
     <t>Organic Whey Protein Concentrate (Regular 80% Protein) | NZMP.com</t>
@@ -3040,7 +3040,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:11.675Z</t>
+    <t>2026-08-14T01:55:25.689Z</t>
   </si>
   <si>
     <t>Lactoferrin - NZMP Dairy Ingredients | NZMP.com</t>
@@ -3055,7 +3055,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-clear-wpi-8855</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:22.459Z</t>
+    <t>2026-08-14T01:55:34.960Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 8855 | NZMP.com</t>
@@ -3070,7 +3070,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-instant-whey-protein-isolate-894</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:30.120Z</t>
+    <t>2026-08-14T01:55:42.802Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Isolate 894 | NZMP.com</t>
@@ -3085,7 +3085,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-instant-whey-protein-isolate-895</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:39.122Z</t>
+    <t>2026-08-14T01:55:50.560Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Isolate 895 | NZMP.com</t>
@@ -3100,7 +3100,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-optibar</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:47.659Z</t>
+    <t>2026-08-14T01:55:59.115Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 894 | NZMP.com</t>
@@ -3115,7 +3115,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825</t>
   </si>
   <si>
-    <t>2026-08-13T23:52:55.259Z</t>
+    <t>2026-08-14T02:06:23.016Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825.html</t>
@@ -3127,7 +3127,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-wpi-895</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:54.879Z</t>
+    <t>2026-08-14T01:56:06.224Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 895 | NZMP.com</t>
@@ -3142,7 +3142,7 @@
     <t>global/en/ingredients/specialty/complex-lipids/milk-phospholipids</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:03.923Z</t>
+    <t>2026-08-14T01:56:59.960Z</t>
   </si>
   <si>
     <t>Milk Phospholipids | NZMP.com</t>
@@ -3157,7 +3157,7 @@
     <t>global/en/ingredients/specialty/complex-lipids/surestart-mfgm-lipids</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:11.920Z</t>
+    <t>2026-08-14T01:57:08.825Z</t>
   </si>
   <si>
     <t>SureStart™ MFGM Lipids | NZMP.com</t>
@@ -3172,7 +3172,7 @@
     <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:15.653Z</t>
+    <t>2026-08-14T02:06:44.578Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817.html</t>
@@ -3184,7 +3184,7 @@
     <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:22.328Z</t>
+    <t>2026-08-14T02:06:54.204Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911.html</t>
@@ -3196,7 +3196,7 @@
     <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:19.760Z</t>
+    <t>2026-08-14T01:57:18.225Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917.html</t>
@@ -3208,7 +3208,7 @@
     <t>global/en/ingredients/specialty/lactoferrin/nzmp-lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:30.370Z</t>
+    <t>2026-08-14T01:57:27.289Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/lactoferrin/nzmp-lactoferrin.html</t>
@@ -3220,7 +3220,7 @@
     <t>global/en/ingredients/specialty/lactoferrin/surestart-lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:40.029Z</t>
+    <t>2026-08-14T01:57:34.423Z</t>
   </si>
   <si>
     <t>Paediatric Lactoferrin - NZMP Dairy Ingredients | NZMP.com</t>
@@ -3232,13 +3232,13 @@
     <t>global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:47.087Z</t>
+    <t>2026-08-14T01:57:41.244Z</t>
   </si>
   <si>
     <t>Galacto-oligosaccharide (GOS) Prebiotic Fibre | NZMP.com</t>
@@ -3253,7 +3253,7 @@
     <t>global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos</t>
   </si>
   <si>
-    <t>2026-08-13T23:53:52.286Z</t>
+    <t>2026-08-14T02:07:30.575Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos.html</t>
@@ -3265,7 +3265,7 @@
     <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/china-dairy-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:22.422Z</t>
+    <t>2026-08-14T02:08:00.359Z</t>
   </si>
   <si>
     <t>Our China Dairy Expertise | NZMP.com</t>
@@ -3277,13 +3277,13 @@
     <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-banner","columns-feature","cards-value"]</t>
+    <t>["columns-banner","columns-feature","cards-value"]</t>
   </si>
   <si>
     <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:30.887Z</t>
+    <t>2026-08-14T02:08:08.772Z</t>
   </si>
   <si>
     <t>Our Europe Dairy Expertise | NZMP.com</t>
@@ -3298,7 +3298,7 @@
     <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/middle-east-africa-dairy-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:42.257Z</t>
+    <t>2026-08-14T02:08:19.133Z</t>
   </si>
   <si>
     <t>Our Middle East &amp; Africa Dairy Expertise | NZMP.com</t>
@@ -3313,7 +3313,7 @@
     <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/south-southeast-asia-dairy-expertise</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:50.940Z</t>
+    <t>2026-08-14T02:08:26.938Z</t>
   </si>
   <si>
     <t>Our South &amp; Southeast Asia Dairy Expertise | NZMP.com</t>
@@ -3328,7 +3328,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/acid-casein-741</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:11.783Z</t>
+    <t>2026-08-14T01:49:20.157Z</t>
   </si>
   <si>
     <t>NZMP™ Mineral Acid Casein 741 | NZMP.com</t>
@@ -3343,7 +3343,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-720</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:20.067Z</t>
+    <t>2026-08-14T01:49:27.566Z</t>
   </si>
   <si>
     <t>NZMP™ Lactic Acid Casein 720 | NZMP.com</t>
@@ -3358,7 +3358,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730</t>
   </si>
   <si>
-    <t>2026-08-13T23:50:51.273Z</t>
+    <t>2026-08-14T02:04:02.621Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730.html</t>
@@ -3370,7 +3370,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/calcium-caseinate-380</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:29.514Z</t>
+    <t>2026-08-14T01:49:36.519Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 380 | NZMP.com</t>
@@ -3385,7 +3385,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-calcium-caseinate-309</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:38.385Z</t>
+    <t>2026-08-14T01:49:43.201Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 309 | NZMP.com</t>
@@ -3400,7 +3400,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-calcium-caseinate-385</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:44.925Z</t>
+    <t>2026-08-14T01:49:50.249Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 385 | NZMP.com</t>
@@ -3415,7 +3415,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-166</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:52.923Z</t>
+    <t>2026-08-14T01:49:58.924Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 166 | NZMP.com</t>
@@ -3430,7 +3430,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-167</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:59.659Z</t>
+    <t>2026-08-14T01:50:06.679Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 167 | NZMP.com</t>
@@ -3445,7 +3445,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-180</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:08.423Z</t>
+    <t>2026-08-14T01:50:14.760Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 180 | NZMP.com</t>
@@ -3460,7 +3460,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/rennet-casein/nzmp-rennet-casein-771</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:15.159Z</t>
+    <t>2026-08-14T01:50:22.923Z</t>
   </si>
   <si>
     <t>NZMP™ Rennet Casein 771 | NZMP.com</t>
@@ -3475,7 +3475,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/rennet-casein/sureprotein-rennet-casein-779</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:22.578Z</t>
+    <t>2026-08-14T01:50:30.844Z</t>
   </si>
   <si>
     <t>NZMP™ Rennet Casein 779 | NZMP.com</t>
